--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484696_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484696_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9476</v>
+        <v>4.3054</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5921</v>
+        <v>2.7022</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3555</v>
+        <v>1.6032</v>
       </c>
       <c r="G2" t="n">
         <v>2.6286</v>
@@ -610,13 +610,13 @@
         <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2195</v>
+        <v>0.5773</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2919</v>
+        <v>0.402</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07240000000000001</v>
+        <v>0.1753</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6314</v>
+        <v>1.928</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2779</v>
+        <v>2.7727</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6465</v>
+        <v>-0.8447</v>
       </c>
       <c r="G3" t="n">
         <v>1.7259</v>
@@ -688,13 +688,13 @@
         <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0944</v>
+        <v>0.2021</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4412</v>
+        <v>0.0536</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3467</v>
+        <v>0.1485</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. HORTELANO ESCRIBA</t>
+          <t>M. GONZALEZ BRU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1328</v>
+        <v>-0.6811</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5953000000000001</v>
+        <v>-1.529</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7281</v>
+        <v>0.8479</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5739</v>
+        <v>0.9851</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3717</v>
+        <v>-1.7718</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2022</v>
+        <v>2.7569</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8241</v>
+        <v>2.2003</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8978</v>
+        <v>-0.4926</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0737</v>
+        <v>2.6929</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.398</v>
+        <v>-1.2152</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.2695</v>
+        <v>-1.2792</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1285</v>
+        <v>0.064</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.4661</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7489</v>
+        <v>-3.6651</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8968</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8107</v>
+        <v>-0.3861</v>
       </c>
       <c r="U5" t="n">
-        <v>1.086</v>
+        <v>-0.3925</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0104</v>
+        <v>0.945</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2907</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3011</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BRU</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1703</v>
+        <v>-1.5105</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9686</v>
+        <v>0.0655</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7983</v>
+        <v>-1.5761</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9851</v>
+        <v>-1.2488</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7718</v>
+        <v>-2.1946</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7569</v>
+        <v>0.9458</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2003</v>
+        <v>1.6836</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4926</v>
+        <v>0.8978</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6929</v>
+        <v>0.7857</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2152</v>
+        <v>-2.9324</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2792</v>
+        <v>-3.0925</v>
       </c>
       <c r="O6" t="n">
-        <v>0.064</v>
+        <v>0.16</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.5498</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.8326</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-3.6651</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2679</v>
+        <v>0.2881</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8258</v>
+        <v>-0.1074</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4421</v>
+        <v>0.3955</v>
       </c>
       <c r="V6" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>C. HORTELANO ESCRIBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0959</v>
+        <v>-1.9853</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4703</v>
+        <v>-0.7369</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6256</v>
+        <v>-1.2484</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2488</v>
+        <v>-1.5739</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1946</v>
+        <v>-0.3717</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9458</v>
+        <v>-1.2022</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6836</v>
+        <v>1.8241</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8978</v>
+        <v>2.8978</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7857</v>
+        <v>-1.0737</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9324</v>
+        <v>-3.398</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.0925</v>
+        <v>-3.2695</v>
       </c>
       <c r="O7" t="n">
-        <v>0.16</v>
+        <v>-0.1285</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5498</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R7" t="n">
         <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2973</v>
+        <v>1.0443</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6433</v>
+        <v>0.4785</v>
       </c>
       <c r="U7" t="n">
-        <v>0.346</v>
+        <v>0.5658</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3219</v>
+        <v>-0.2907</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1342</v>
+        <v>-2.8898</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4068</v>
+        <v>-0.0633</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7274</v>
+        <v>-2.8265</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1474</v>
@@ -1078,13 +1078,13 @@
         <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0472</v>
+        <v>0.1972</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2941</v>
+        <v>0.0494</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2469</v>
+        <v>0.1478</v>
       </c>
       <c r="V8" t="n">
         <v>-2.8559</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4235</v>
+        <v>-3.6376</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0735</v>
+        <v>-3.3619</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.35</v>
+        <v>-0.2757</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6109</v>
@@ -1156,13 +1156,13 @@
         <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0063</v>
+        <v>-0.2204</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2006</v>
+        <v>-0.0878</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2069</v>
+        <v>-0.1325</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6231</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9524</v>
+        <v>-4.897</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4912</v>
+        <v>-1.6835</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4613</v>
+        <v>-3.2135</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0588</v>
@@ -1234,13 +1234,13 @@
         <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.276</v>
+        <v>-0.2206</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0565</v>
+        <v>-0.2489</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2195</v>
+        <v>0.0283</v>
       </c>
       <c r="V10" t="n">
         <v>-2.5339</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7137</v>
+        <v>-5.1062</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4949</v>
+        <v>-4.1103</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2188</v>
+        <v>-0.9959</v>
       </c>
       <c r="G11" t="n">
         <v>-4.066</v>
@@ -1312,13 +1312,13 @@
         <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6477</v>
+        <v>-1.0402</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0648</v>
+        <v>-0.6802</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5829</v>
+        <v>-0.3599</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2813</v>
+        <v>-7.3005</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9097</v>
+        <v>-4.8546</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3716</v>
+        <v>-2.4459</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4747</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2147</v>
+        <v>-0.234</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3688</v>
+        <v>-0.3137</v>
       </c>
       <c r="U12" t="n">
-        <v>0.154</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2774</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-22</v>
+        <v>-21.4495</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.0246</v>
+        <v>-10.474</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.9755</v>
+        <v>-10.9756</v>
       </c>
       <c r="G13" t="n">
         <v>-8.5158</v>
@@ -1441,10 +1441,10 @@
         <v>2.565700000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>9.810699999999999</v>
+        <v>9.810700000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>7.0829</v>
+        <v>7.082900000000001</v>
       </c>
       <c r="L13" t="n">
         <v>2.7276</v>
@@ -1468,13 +1468,13 @@
         <v>14.6606</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7352000000000004</v>
+        <v>-0.1848999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3913</v>
+        <v>-0.8406</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6558</v>
+        <v>0.6559999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-6.3349</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.1359</v>
+        <v>11.2961</v>
       </c>
       <c r="E14" t="n">
-        <v>9.540900000000001</v>
+        <v>9.444699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.595</v>
+        <v>1.8514</v>
       </c>
       <c r="G14" t="n">
         <v>6.4308</v>
@@ -1546,13 +1546,13 @@
         <v>2.5656</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2391</v>
+        <v>0.3993</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0196</v>
+        <v>-0.1157</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2586</v>
+        <v>0.5151</v>
       </c>
       <c r="V14" t="n">
         <v>1.9005</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.1094</v>
+        <v>9.026899999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>8.1149</v>
+        <v>6.6726</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9944</v>
+        <v>2.3543</v>
       </c>
       <c r="G15" t="n">
         <v>2.9374</v>
@@ -1624,13 +1624,13 @@
         <v>2.7489</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8892</v>
+        <v>0.8067</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6282</v>
+        <v>0.1859</v>
       </c>
       <c r="U15" t="n">
-        <v>0.261</v>
+        <v>0.6208</v>
       </c>
       <c r="V15" t="n">
         <v>2.5339</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8264</v>
+        <v>5.1964</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7793</v>
+        <v>1.9716</v>
       </c>
       <c r="F16" t="n">
-        <v>3.047</v>
+        <v>3.2248</v>
       </c>
       <c r="G16" t="n">
         <v>3.4261</v>
@@ -1702,13 +1702,13 @@
         <v>2.1991</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2045</v>
+        <v>0.1655</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6056</v>
+        <v>-0.4133</v>
       </c>
       <c r="U16" t="n">
-        <v>0.401</v>
+        <v>0.5788</v>
       </c>
       <c r="V16" t="n">
         <v>0.3219</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4532</v>
+        <v>4.3711</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5062</v>
+        <v>1.8908</v>
       </c>
       <c r="F17" t="n">
-        <v>1.947</v>
+        <v>2.4803</v>
       </c>
       <c r="G17" t="n">
         <v>3.4084</v>
@@ -1780,13 +1780,13 @@
         <v>2.7489</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8715000000000001</v>
+        <v>0.0464</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8258</v>
+        <v>-0.4412</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0457</v>
+        <v>0.4875</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5</v>
+        <v>1.7719</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3574</v>
+        <v>-0.6309</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1426</v>
+        <v>2.4028</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7437</v>
+        <v>-0.7173</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6222</v>
+        <v>0.1098</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8785</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4624</v>
+        <v>0.1851</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4804</v>
+        <v>1.3005</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9428</v>
+        <v>-1.1154</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.206</v>
+        <v>-0.9024</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1418</v>
+        <v>-1.1907</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0643</v>
+        <v>0.2882</v>
       </c>
       <c r="P18" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6493</v>
+        <v>2.7489</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5106</v>
+        <v>0.3346</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4344</v>
+        <v>-0.2217</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0762</v>
+        <v>0.5563</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6231</v>
+        <v>0.3219</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0887</v>
+        <v>0.8727</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4002</v>
+        <v>-0.3733</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4889</v>
+        <v>1.246</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7173</v>
+        <v>-0.7437</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1098</v>
+        <v>-2.6222</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8270999999999999</v>
+        <v>1.8785</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1851</v>
+        <v>0.4624</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3005</v>
+        <v>-1.4804</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1154</v>
+        <v>1.9428</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9024</v>
+        <v>-1.206</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1907</v>
+        <v>-1.1418</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2882</v>
+        <v>-0.0643</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8326</v>
+        <v>0.733</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7489</v>
+        <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3485</v>
+        <v>0.8833</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9909</v>
+        <v>0.7036</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6424</v>
+        <v>0.1797</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4183</v>
+        <v>0.5683</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6629</v>
+        <v>-0.5668</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0812</v>
+        <v>1.1351</v>
       </c>
       <c r="G20" t="n">
         <v>0.7054</v>
@@ -2014,13 +2014,13 @@
         <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1039</v>
+        <v>0.0462</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2202</v>
+        <v>-0.1241</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1164</v>
+        <v>0.1702</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2098</v>
+        <v>-0.7864</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0752</v>
+        <v>-0.2098</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1346</v>
+        <v>-0.5765</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3851</v>
@@ -2092,13 +2092,13 @@
         <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3874</v>
+        <v>0.036</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9359</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4515</v>
+        <v>0.1065</v>
       </c>
       <c r="V21" t="n">
         <v>2.212</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q. GJENERALI</t>
+          <t>V. SORIANO INCHAURRAGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5567</v>
+        <v>-1.9455</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3948</v>
+        <v>-2.4175</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1619</v>
+        <v>0.472</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0156</v>
+        <v>-0.432</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3618</v>
+        <v>-0.0761</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6538</v>
+        <v>-0.356</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8095</v>
+        <v>1.2304</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.22</v>
+        <v>1.1054</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5895</v>
+        <v>0.125</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.206</v>
+        <v>-1.6624</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1418</v>
+        <v>-1.1815</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0643</v>
+        <v>-0.481</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3665</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R22" t="n">
         <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1746</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0746</v>
+        <v>-0.276</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0999</v>
+        <v>0.3673</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. SORIANO INCHAURRAGA</t>
+          <t>Q. GJENERALI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6856</v>
+        <v>-2.1123</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8021</v>
+        <v>-2.2025</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1165</v>
+        <v>0.0902</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.432</v>
+        <v>-2.0156</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0761</v>
+        <v>-1.3618</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.356</v>
+        <v>-0.6538</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2304</v>
+        <v>-0.8095</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1054</v>
+        <v>-0.22</v>
       </c>
       <c r="L23" t="n">
-        <v>0.125</v>
+        <v>-0.5895</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6624</v>
+        <v>-1.206</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1815</v>
+        <v>-1.1418</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.481</v>
+        <v>-0.0643</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
         <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6489</v>
+        <v>0.2698</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6606</v>
+        <v>0.1177</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0118</v>
+        <v>0.1521</v>
       </c>
       <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="X23" t="n">
         <v>-0.3219</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-0.6231</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.3011</v>
       </c>
     </row>
     <row r="24">
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0797</v>
+        <v>-3.6951</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.988</v>
+        <v>-2.6034</v>
       </c>
       <c r="F24" t="n">
         <v>-1.0917</v>
@@ -2326,10 +2326,10 @@
         <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1644</v>
+        <v>0.2202</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3854</v>
+        <v>-0.0007</v>
       </c>
       <c r="U24" t="n">
         <v>0.221</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>22.0001</v>
+        <v>24.5641</v>
       </c>
       <c r="E25" t="n">
         <v>10.9755</v>
       </c>
       <c r="F25" t="n">
-        <v>11.0244</v>
+        <v>13.5887</v>
       </c>
       <c r="G25" t="n">
-        <v>8.515800000000002</v>
+        <v>8.5158</v>
       </c>
       <c r="H25" t="n">
         <v>11.0815</v>
@@ -2404,19 +2404,19 @@
         <v>21.0747</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7351999999999997</v>
+        <v>3.2993</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6559999999999997</v>
+        <v>-0.656</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3913</v>
+        <v>3.9553</v>
       </c>
       <c r="V25" t="n">
         <v>6.3348</v>
       </c>
       <c r="W25" t="n">
-        <v>7.9652</v>
+        <v>7.965200000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-1.6305</v>
